--- a/Team-Data/2013-14/12-15-2013-14.xlsx
+++ b/Team-Data/2013-14/12-15-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,16 +806,16 @@
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE2" t="n">
         <v>12</v>
       </c>
       <c r="AF2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH2" t="n">
         <v>21</v>
@@ -760,7 +827,7 @@
         <v>21</v>
       </c>
       <c r="AK2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL2" t="n">
         <v>9</v>
@@ -769,7 +836,7 @@
         <v>10</v>
       </c>
       <c r="AN2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO2" t="n">
         <v>21</v>
@@ -796,7 +863,7 @@
         <v>15</v>
       </c>
       <c r="AW2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX2" t="n">
         <v>26</v>
@@ -811,7 +878,7 @@
         <v>24</v>
       </c>
       <c r="BB2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC2" t="n">
         <v>15</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-15-2013-14</t>
+          <t>2013-12-15</t>
         </is>
       </c>
     </row>
@@ -924,13 +991,13 @@
         <v>2</v>
       </c>
       <c r="AE3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AH3" t="n">
         <v>24</v>
@@ -951,7 +1018,7 @@
         <v>24</v>
       </c>
       <c r="AN3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO3" t="n">
         <v>25</v>
@@ -960,31 +1027,31 @@
         <v>27</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR3" t="n">
         <v>24</v>
       </c>
       <c r="AS3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU3" t="n">
         <v>30</v>
       </c>
       <c r="AV3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW3" t="n">
         <v>24</v>
       </c>
       <c r="AX3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ3" t="n">
         <v>20</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-15-2013-14</t>
+          <t>2013-12-15</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-6.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE4" t="n">
         <v>24</v>
@@ -1115,7 +1182,7 @@
         <v>24</v>
       </c>
       <c r="AH4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI4" t="n">
         <v>28</v>
@@ -1142,28 +1209,28 @@
         <v>5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR4" t="n">
         <v>21</v>
       </c>
       <c r="AS4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT4" t="n">
         <v>22</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>23</v>
       </c>
       <c r="AU4" t="n">
         <v>25</v>
       </c>
       <c r="AV4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW4" t="n">
         <v>27</v>
       </c>
       <c r="AX4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY4" t="n">
         <v>7</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-15-2013-14</t>
+          <t>2013-12-15</t>
         </is>
       </c>
     </row>
@@ -1285,13 +1352,13 @@
         <v>-2.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE5" t="n">
         <v>18</v>
       </c>
       <c r="AF5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG5" t="n">
         <v>19</v>
@@ -1333,10 +1400,10 @@
         <v>13</v>
       </c>
       <c r="AT5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AV5" t="n">
         <v>2</v>
@@ -1348,7 +1415,7 @@
         <v>9</v>
       </c>
       <c r="AY5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ5" t="n">
         <v>5</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-15-2013-14</t>
+          <t>2013-12-15</t>
         </is>
       </c>
     </row>
@@ -1467,19 +1534,19 @@
         <v>-1.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AE6" t="n">
         <v>20</v>
       </c>
       <c r="AF6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG6" t="n">
         <v>20</v>
       </c>
       <c r="AH6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI6" t="n">
         <v>27</v>
@@ -1509,7 +1576,7 @@
         <v>9</v>
       </c>
       <c r="AR6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS6" t="n">
         <v>8</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-15-2013-14</t>
+          <t>2013-12-15</t>
         </is>
       </c>
     </row>
@@ -1649,13 +1716,13 @@
         <v>-5.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE7" t="n">
         <v>20</v>
       </c>
       <c r="AF7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG7" t="n">
         <v>23</v>
@@ -1676,7 +1743,7 @@
         <v>20</v>
       </c>
       <c r="AM7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AN7" t="n">
         <v>18</v>
@@ -1691,7 +1758,7 @@
         <v>20</v>
       </c>
       <c r="AR7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS7" t="n">
         <v>16</v>
@@ -1712,7 +1779,7 @@
         <v>25</v>
       </c>
       <c r="AY7" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AZ7" t="n">
         <v>6</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-15-2013-14</t>
+          <t>2013-12-15</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>1.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE8" t="n">
         <v>8</v>
@@ -1849,7 +1916,7 @@
         <v>5</v>
       </c>
       <c r="AJ8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK8" t="n">
         <v>10</v>
@@ -1864,19 +1931,19 @@
         <v>7</v>
       </c>
       <c r="AO8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP8" t="n">
         <v>26</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR8" t="n">
         <v>25</v>
       </c>
       <c r="AS8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT8" t="n">
         <v>25</v>
@@ -1888,7 +1955,7 @@
         <v>12</v>
       </c>
       <c r="AW8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX8" t="n">
         <v>24</v>
@@ -1897,13 +1964,13 @@
         <v>5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA8" t="n">
         <v>26</v>
       </c>
       <c r="BB8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC8" t="n">
         <v>12</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-15-2013-14</t>
+          <t>2013-12-15</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F9" t="n">
         <v>9</v>
       </c>
       <c r="G9" t="n">
-        <v>0.609</v>
+        <v>0.591</v>
       </c>
       <c r="H9" t="n">
         <v>48</v>
@@ -1956,52 +2023,52 @@
         <v>84.8</v>
       </c>
       <c r="K9" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L9" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="M9" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="N9" t="n">
-        <v>0.366</v>
+        <v>0.37</v>
       </c>
       <c r="O9" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="P9" t="n">
-        <v>25.7</v>
+        <v>25.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.71</v>
+        <v>0.708</v>
       </c>
       <c r="R9" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="S9" t="n">
-        <v>33.4</v>
+        <v>33.3</v>
       </c>
       <c r="T9" t="n">
-        <v>46.3</v>
+        <v>46.1</v>
       </c>
       <c r="U9" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="V9" t="n">
-        <v>14.6</v>
+        <v>14.4</v>
       </c>
       <c r="W9" t="n">
         <v>7.1</v>
       </c>
       <c r="X9" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="AA9" t="n">
         <v>21.4</v>
@@ -2010,16 +2077,16 @@
         <v>102.1</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AD9" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AE9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG9" t="n">
         <v>8</v>
@@ -2028,31 +2095,31 @@
         <v>24</v>
       </c>
       <c r="AI9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK9" t="n">
         <v>17</v>
       </c>
       <c r="AL9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AM9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AN9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AO9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP9" t="n">
         <v>7</v>
       </c>
       <c r="AQ9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR9" t="n">
         <v>5</v>
@@ -2067,28 +2134,28 @@
         <v>14</v>
       </c>
       <c r="AV9" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AW9" t="n">
         <v>21</v>
       </c>
       <c r="AX9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY9" t="n">
         <v>22</v>
       </c>
       <c r="AZ9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB9" t="n">
         <v>12</v>
       </c>
       <c r="BC9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-15-2013-14</t>
+          <t>2013-12-15</t>
         </is>
       </c>
     </row>
@@ -2117,118 +2184,118 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E10" t="n">
         <v>11</v>
       </c>
       <c r="F10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G10" t="n">
-        <v>0.44</v>
+        <v>0.458</v>
       </c>
       <c r="H10" t="n">
-        <v>48.6</v>
+        <v>48.4</v>
       </c>
       <c r="I10" t="n">
-        <v>38.4</v>
+        <v>38.2</v>
       </c>
       <c r="J10" t="n">
-        <v>85</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.452</v>
+        <v>0.451</v>
       </c>
       <c r="L10" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="M10" t="n">
-        <v>19.6</v>
+        <v>19.8</v>
       </c>
       <c r="N10" t="n">
-        <v>0.31</v>
+        <v>0.314</v>
       </c>
       <c r="O10" t="n">
         <v>17</v>
       </c>
       <c r="P10" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="Q10" t="n">
         <v>0.672</v>
       </c>
       <c r="R10" t="n">
-        <v>14</v>
+        <v>13.8</v>
       </c>
       <c r="S10" t="n">
-        <v>30.4</v>
+        <v>30.2</v>
       </c>
       <c r="T10" t="n">
-        <v>44.4</v>
+        <v>44</v>
       </c>
       <c r="U10" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="V10" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="W10" t="n">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="X10" t="n">
         <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z10" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AA10" t="n">
         <v>20.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>99.90000000000001</v>
+        <v>99.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1.2</v>
+        <v>-1.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF10" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AG10" t="n">
         <v>16</v>
       </c>
       <c r="AH10" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AI10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AK10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AL10" t="n">
         <v>26</v>
       </c>
       <c r="AM10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AN10" t="n">
         <v>29</v>
       </c>
       <c r="AO10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP10" t="n">
         <v>8</v>
@@ -2243,16 +2310,16 @@
         <v>25</v>
       </c>
       <c r="AT10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU10" t="n">
         <v>22</v>
       </c>
       <c r="AV10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AX10" t="n">
         <v>11</v>
@@ -2261,13 +2328,13 @@
         <v>16</v>
       </c>
       <c r="AZ10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA10" t="n">
+        <v>15</v>
+      </c>
+      <c r="BB10" t="n">
         <v>16</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>15</v>
       </c>
       <c r="BC10" t="n">
         <v>17</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-15-2013-14</t>
+          <t>2013-12-15</t>
         </is>
       </c>
     </row>
@@ -2299,88 +2366,88 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E11" t="n">
         <v>13</v>
       </c>
       <c r="F11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G11" t="n">
-        <v>0.52</v>
+        <v>0.542</v>
       </c>
       <c r="H11" t="n">
         <v>48.4</v>
       </c>
       <c r="I11" t="n">
-        <v>38.3</v>
+        <v>38.5</v>
       </c>
       <c r="J11" t="n">
-        <v>82.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>0.466</v>
+        <v>0.467</v>
       </c>
       <c r="L11" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M11" t="n">
         <v>23.5</v>
       </c>
       <c r="N11" t="n">
-        <v>0.416</v>
+        <v>0.412</v>
       </c>
       <c r="O11" t="n">
-        <v>16.6</v>
+        <v>16.3</v>
       </c>
       <c r="P11" t="n">
-        <v>22.7</v>
+        <v>22.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.732</v>
+        <v>0.734</v>
       </c>
       <c r="R11" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="S11" t="n">
-        <v>34.6</v>
+        <v>34.4</v>
       </c>
       <c r="T11" t="n">
-        <v>45</v>
+        <v>44.8</v>
       </c>
       <c r="U11" t="n">
-        <v>22.4</v>
+        <v>22.6</v>
       </c>
       <c r="V11" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="W11" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X11" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z11" t="n">
         <v>22.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="AB11" t="n">
         <v>103</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AF11" t="n">
         <v>12</v>
@@ -2389,10 +2456,10 @@
         <v>11</v>
       </c>
       <c r="AH11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ11" t="n">
         <v>16</v>
@@ -2401,19 +2468,19 @@
         <v>5</v>
       </c>
       <c r="AL11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM11" t="n">
         <v>8</v>
       </c>
       <c r="AN11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO11" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP11" t="n">
         <v>17</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>15</v>
       </c>
       <c r="AQ11" t="n">
         <v>22</v>
@@ -2428,7 +2495,7 @@
         <v>8</v>
       </c>
       <c r="AU11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV11" t="n">
         <v>28</v>
@@ -2449,7 +2516,7 @@
         <v>17</v>
       </c>
       <c r="BB11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC11" t="n">
         <v>9</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-15-2013-14</t>
+          <t>2013-12-15</t>
         </is>
       </c>
     </row>
@@ -2481,85 +2548,85 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E12" t="n">
         <v>16</v>
       </c>
       <c r="F12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G12" t="n">
-        <v>0.64</v>
+        <v>0.667</v>
       </c>
       <c r="H12" t="n">
         <v>48.6</v>
       </c>
       <c r="I12" t="n">
-        <v>37.3</v>
+        <v>37.5</v>
       </c>
       <c r="J12" t="n">
-        <v>78.90000000000001</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.472</v>
+        <v>0.475</v>
       </c>
       <c r="L12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="M12" t="n">
         <v>27.4</v>
       </c>
       <c r="N12" t="n">
-        <v>0.357</v>
+        <v>0.361</v>
       </c>
       <c r="O12" t="n">
         <v>22.7</v>
       </c>
       <c r="P12" t="n">
-        <v>32.6</v>
+        <v>32.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.697</v>
+        <v>0.702</v>
       </c>
       <c r="R12" t="n">
         <v>11.3</v>
       </c>
       <c r="S12" t="n">
-        <v>35.2</v>
+        <v>35.4</v>
       </c>
       <c r="T12" t="n">
-        <v>46.5</v>
+        <v>46.7</v>
       </c>
       <c r="U12" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="V12" t="n">
         <v>17.7</v>
       </c>
       <c r="W12" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="Y12" t="n">
         <v>5.7</v>
       </c>
       <c r="Z12" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="AA12" t="n">
         <v>25.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>107</v>
+        <v>107.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE12" t="n">
         <v>6</v>
@@ -2571,10 +2638,10 @@
         <v>6</v>
       </c>
       <c r="AH12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ12" t="n">
         <v>28</v>
@@ -2589,7 +2656,7 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AO12" t="n">
         <v>1</v>
@@ -2610,16 +2677,16 @@
         <v>2</v>
       </c>
       <c r="AU12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV12" t="n">
         <v>29</v>
       </c>
       <c r="AW12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AX12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY12" t="n">
         <v>21</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-15-2013-14</t>
+          <t>2013-12-15</t>
         </is>
       </c>
     </row>
@@ -2741,10 +2808,10 @@
         <v>8.300000000000001</v>
       </c>
       <c r="AD13" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF13" t="n">
         <v>1</v>
@@ -2774,10 +2841,10 @@
         <v>12</v>
       </c>
       <c r="AO13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ13" t="n">
         <v>6</v>
@@ -2789,13 +2856,13 @@
         <v>4</v>
       </c>
       <c r="AT13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AU13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW13" t="n">
         <v>19</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-15-2013-14</t>
+          <t>2013-12-15</t>
         </is>
       </c>
     </row>
@@ -2929,10 +2996,10 @@
         <v>6</v>
       </c>
       <c r="AF14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH14" t="n">
         <v>23</v>
@@ -2947,7 +3014,7 @@
         <v>7</v>
       </c>
       <c r="AL14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM14" t="n">
         <v>7</v>
@@ -2962,7 +3029,7 @@
         <v>2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR14" t="n">
         <v>23</v>
@@ -2977,7 +3044,7 @@
         <v>3</v>
       </c>
       <c r="AV14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW14" t="n">
         <v>13</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-15-2013-14</t>
+          <t>2013-12-15</t>
         </is>
       </c>
     </row>
@@ -3105,22 +3172,22 @@
         <v>-3</v>
       </c>
       <c r="AD15" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG15" t="n">
         <v>14</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>15</v>
       </c>
       <c r="AH15" t="n">
         <v>24</v>
       </c>
       <c r="AI15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ15" t="n">
         <v>5</v>
@@ -3135,7 +3202,7 @@
         <v>2</v>
       </c>
       <c r="AN15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO15" t="n">
         <v>26</v>
@@ -3180,7 +3247,7 @@
         <v>14</v>
       </c>
       <c r="BC15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-15-2013-14</t>
+          <t>2013-12-15</t>
         </is>
       </c>
     </row>
@@ -3209,25 +3276,25 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G16" t="n">
-        <v>0.435</v>
+        <v>0.455</v>
       </c>
       <c r="H16" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I16" t="n">
         <v>36.4</v>
       </c>
       <c r="J16" t="n">
-        <v>80.8</v>
+        <v>80.7</v>
       </c>
       <c r="K16" t="n">
         <v>0.451</v>
@@ -3242,34 +3309,34 @@
         <v>0.34</v>
       </c>
       <c r="O16" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="P16" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.767</v>
+        <v>0.769</v>
       </c>
       <c r="R16" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="S16" t="n">
-        <v>30.7</v>
+        <v>30.5</v>
       </c>
       <c r="T16" t="n">
-        <v>41.3</v>
+        <v>41.1</v>
       </c>
       <c r="U16" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="V16" t="n">
-        <v>13.9</v>
+        <v>14.1</v>
       </c>
       <c r="W16" t="n">
         <v>7</v>
       </c>
       <c r="X16" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Y16" t="n">
         <v>5.2</v>
@@ -3278,28 +3345,28 @@
         <v>19.9</v>
       </c>
       <c r="AA16" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AB16" t="n">
         <v>93.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>-3.7</v>
+        <v>-3.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AE16" t="n">
         <v>18</v>
       </c>
       <c r="AF16" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AG16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI16" t="n">
         <v>20</v>
@@ -3308,7 +3375,7 @@
         <v>25</v>
       </c>
       <c r="AK16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL16" t="n">
         <v>29</v>
@@ -3317,34 +3384,34 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO16" t="n">
         <v>20</v>
       </c>
       <c r="AP16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ16" t="n">
         <v>12</v>
       </c>
       <c r="AR16" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AS16" t="n">
         <v>24</v>
       </c>
       <c r="AT16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW16" t="n">
         <v>22</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>16</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>23</v>
       </c>
       <c r="AX16" t="n">
         <v>27</v>
@@ -3362,7 +3429,7 @@
         <v>26</v>
       </c>
       <c r="BC16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-15-2013-14</t>
+          <t>2013-12-15</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>7</v>
       </c>
       <c r="AD17" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE17" t="n">
         <v>5</v>
@@ -3484,7 +3551,7 @@
         <v>24</v>
       </c>
       <c r="AI17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ17" t="n">
         <v>30</v>
@@ -3505,10 +3572,10 @@
         <v>8</v>
       </c>
       <c r="AP17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR17" t="n">
         <v>30</v>
@@ -3526,7 +3593,7 @@
         <v>18</v>
       </c>
       <c r="AW17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX17" t="n">
         <v>8</v>
@@ -3541,10 +3608,10 @@
         <v>11</v>
       </c>
       <c r="BB17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-15-2013-14</t>
+          <t>2013-12-15</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-8.9</v>
       </c>
       <c r="AD18" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3663,7 +3730,7 @@
         <v>30</v>
       </c>
       <c r="AH18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI18" t="n">
         <v>29</v>
@@ -3681,7 +3748,7 @@
         <v>22</v>
       </c>
       <c r="AN18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO18" t="n">
         <v>28</v>
@@ -3690,10 +3757,10 @@
         <v>28</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS18" t="n">
         <v>28</v>
@@ -3702,10 +3769,10 @@
         <v>28</v>
       </c>
       <c r="AU18" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AV18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW18" t="n">
         <v>25</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-15-2013-14</t>
+          <t>2013-12-15</t>
         </is>
       </c>
     </row>
@@ -3755,97 +3822,97 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F19" t="n">
         <v>12</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5</v>
+        <v>0.478</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
       </c>
       <c r="I19" t="n">
-        <v>37.8</v>
+        <v>37.9</v>
       </c>
       <c r="J19" t="n">
-        <v>88.8</v>
+        <v>89.2</v>
       </c>
       <c r="K19" t="n">
-        <v>0.425</v>
+        <v>0.424</v>
       </c>
       <c r="L19" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="M19" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="N19" t="n">
-        <v>0.342</v>
+        <v>0.336</v>
       </c>
       <c r="O19" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="P19" t="n">
-        <v>27</v>
+        <v>27.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="R19" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="S19" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T19" t="n">
-        <v>45.1</v>
+        <v>45.2</v>
       </c>
       <c r="U19" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="V19" t="n">
-        <v>14.4</v>
+        <v>14.7</v>
       </c>
       <c r="W19" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="X19" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Y19" t="n">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="Z19" t="n">
         <v>16.9</v>
       </c>
       <c r="AA19" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>105.5</v>
+        <v>105.7</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AE19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG19" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AH19" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AI19" t="n">
         <v>12</v>
@@ -3863,7 +3930,7 @@
         <v>6</v>
       </c>
       <c r="AN19" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AO19" t="n">
         <v>3</v>
@@ -3872,7 +3939,7 @@
         <v>3</v>
       </c>
       <c r="AQ19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR19" t="n">
         <v>3</v>
@@ -3887,16 +3954,16 @@
         <v>8</v>
       </c>
       <c r="AV19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AW19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX19" t="n">
         <v>30</v>
       </c>
       <c r="AY19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AZ19" t="n">
         <v>1</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-15-2013-14</t>
+          <t>2013-12-15</t>
         </is>
       </c>
     </row>
@@ -3937,25 +4004,25 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E20" t="n">
         <v>11</v>
       </c>
       <c r="F20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5</v>
+        <v>0.524</v>
       </c>
       <c r="H20" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="I20" t="n">
-        <v>39.1</v>
+        <v>39.2</v>
       </c>
       <c r="J20" t="n">
-        <v>86.59999999999999</v>
+        <v>86.7</v>
       </c>
       <c r="K20" t="n">
         <v>0.452</v>
@@ -3964,40 +4031,40 @@
         <v>6.6</v>
       </c>
       <c r="M20" t="n">
-        <v>17.1</v>
+        <v>16.8</v>
       </c>
       <c r="N20" t="n">
-        <v>0.388</v>
+        <v>0.395</v>
       </c>
       <c r="O20" t="n">
-        <v>18</v>
+        <v>18.3</v>
       </c>
       <c r="P20" t="n">
-        <v>23.3</v>
+        <v>23.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.774</v>
+        <v>0.779</v>
       </c>
       <c r="R20" t="n">
-        <v>13.2</v>
+        <v>13.4</v>
       </c>
       <c r="S20" t="n">
-        <v>29.7</v>
+        <v>30</v>
       </c>
       <c r="T20" t="n">
-        <v>42.9</v>
+        <v>43.4</v>
       </c>
       <c r="U20" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="V20" t="n">
         <v>13.5</v>
       </c>
       <c r="W20" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="X20" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="Y20" t="n">
         <v>6.3</v>
@@ -4006,22 +4073,22 @@
         <v>21.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>103</v>
+        <v>103.4</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AE20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG20" t="n">
         <v>12</v>
@@ -4036,7 +4103,7 @@
         <v>3</v>
       </c>
       <c r="AK20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL20" t="n">
         <v>23</v>
@@ -4045,16 +4112,16 @@
         <v>27</v>
       </c>
       <c r="AN20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO20" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AP20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR20" t="n">
         <v>2</v>
@@ -4063,31 +4130,31 @@
         <v>26</v>
       </c>
       <c r="AT20" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AU20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV20" t="n">
         <v>3</v>
       </c>
       <c r="AW20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX20" t="n">
         <v>1</v>
       </c>
       <c r="AY20" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AZ20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA20" t="n">
         <v>18</v>
       </c>
       <c r="BB20" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BC20" t="n">
         <v>13</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-15-2013-14</t>
+          <t>2013-12-15</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-3.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE21" t="n">
         <v>25</v>
@@ -4206,7 +4273,7 @@
         <v>26</v>
       </c>
       <c r="AG21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH21" t="n">
         <v>18</v>
@@ -4239,7 +4306,7 @@
         <v>8</v>
       </c>
       <c r="AR21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS21" t="n">
         <v>30</v>
@@ -4257,7 +4324,7 @@
         <v>7</v>
       </c>
       <c r="AX21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY21" t="n">
         <v>7</v>
@@ -4272,7 +4339,7 @@
         <v>25</v>
       </c>
       <c r="BC21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-15-2013-14</t>
+          <t>2013-12-15</t>
         </is>
       </c>
     </row>
@@ -4301,97 +4368,97 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F22" t="n">
         <v>4</v>
       </c>
       <c r="G22" t="n">
-        <v>0.826</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I22" t="n">
         <v>38.8</v>
       </c>
       <c r="J22" t="n">
-        <v>83.09999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>0.467</v>
+        <v>0.468</v>
       </c>
       <c r="L22" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="M22" t="n">
         <v>18.6</v>
       </c>
       <c r="N22" t="n">
-        <v>0.334</v>
+        <v>0.337</v>
       </c>
       <c r="O22" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="P22" t="n">
-        <v>26.7</v>
+        <v>27</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.821</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="R22" t="n">
         <v>11.4</v>
       </c>
       <c r="S22" t="n">
-        <v>35.9</v>
+        <v>36</v>
       </c>
       <c r="T22" t="n">
-        <v>47.3</v>
+        <v>47.4</v>
       </c>
       <c r="U22" t="n">
         <v>21.9</v>
       </c>
       <c r="V22" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="W22" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="X22" t="n">
         <v>6.4</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Z22" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AD22" t="n">
         <v>22</v>
       </c>
-      <c r="AA22" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>105.7</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>15</v>
-      </c>
       <c r="AE22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF22" t="n">
         <v>2</v>
       </c>
       <c r="AG22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI22" t="n">
         <v>6</v>
@@ -4409,7 +4476,7 @@
         <v>23</v>
       </c>
       <c r="AN22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO22" t="n">
         <v>2</v>
@@ -4436,10 +4503,10 @@
         <v>26</v>
       </c>
       <c r="AW22" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AX22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY22" t="n">
         <v>10</v>
@@ -4448,13 +4515,13 @@
         <v>24</v>
       </c>
       <c r="BA22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BB22" t="n">
         <v>3</v>
       </c>
       <c r="BC22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-15-2013-14</t>
+          <t>2013-12-15</t>
         </is>
       </c>
     </row>
@@ -4483,19 +4550,19 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E23" t="n">
         <v>7</v>
       </c>
       <c r="F23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G23" t="n">
-        <v>0.292</v>
+        <v>0.304</v>
       </c>
       <c r="H23" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="I23" t="n">
         <v>37</v>
@@ -4510,46 +4577,46 @@
         <v>7.7</v>
       </c>
       <c r="M23" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="N23" t="n">
-        <v>0.354</v>
+        <v>0.357</v>
       </c>
       <c r="O23" t="n">
         <v>15.9</v>
       </c>
       <c r="P23" t="n">
-        <v>21</v>
+        <v>20.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.759</v>
+        <v>0.765</v>
       </c>
       <c r="R23" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>32.7</v>
+        <v>32.5</v>
       </c>
       <c r="T23" t="n">
-        <v>41.8</v>
+        <v>41.7</v>
       </c>
       <c r="U23" t="n">
         <v>20.4</v>
       </c>
       <c r="V23" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="W23" t="n">
         <v>8</v>
       </c>
       <c r="X23" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="Y23" t="n">
         <v>5.9</v>
       </c>
       <c r="Z23" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AA23" t="n">
         <v>18.6</v>
@@ -4561,19 +4628,19 @@
         <v>-4.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AE23" t="n">
         <v>25</v>
       </c>
       <c r="AF23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG23" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AH23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI23" t="n">
         <v>18</v>
@@ -4600,34 +4667,34 @@
         <v>25</v>
       </c>
       <c r="AQ23" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AR23" t="n">
         <v>27</v>
       </c>
       <c r="AS23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AT23" t="n">
         <v>21</v>
       </c>
       <c r="AU23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV23" t="n">
+        <v>25</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY23" t="n">
         <v>23</v>
       </c>
-      <c r="AW23" t="n">
-        <v>16</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>21</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>24</v>
-      </c>
       <c r="AZ23" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA23" t="n">
         <v>29</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-15-2013-14</t>
+          <t>2013-12-15</t>
         </is>
       </c>
     </row>
@@ -4779,13 +4846,13 @@
         <v>22</v>
       </c>
       <c r="AP24" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AQ24" t="n">
         <v>28</v>
       </c>
       <c r="AR24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS24" t="n">
         <v>6</v>
@@ -4800,10 +4867,10 @@
         <v>30</v>
       </c>
       <c r="AW24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY24" t="n">
         <v>29</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-15-2013-14</t>
+          <t>2013-12-15</t>
         </is>
       </c>
     </row>
@@ -4847,64 +4914,64 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F25" t="n">
         <v>9</v>
       </c>
       <c r="G25" t="n">
-        <v>0.609</v>
+        <v>0.591</v>
       </c>
       <c r="H25" t="n">
         <v>48.2</v>
       </c>
       <c r="I25" t="n">
-        <v>38</v>
+        <v>38.1</v>
       </c>
       <c r="J25" t="n">
-        <v>81.59999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="K25" t="n">
-        <v>0.465</v>
+        <v>0.466</v>
       </c>
       <c r="L25" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>25.2</v>
+        <v>25.1</v>
       </c>
       <c r="N25" t="n">
-        <v>0.375</v>
+        <v>0.37</v>
       </c>
       <c r="O25" t="n">
-        <v>17.2</v>
+        <v>17</v>
       </c>
       <c r="P25" t="n">
-        <v>23.2</v>
+        <v>22.7</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.742</v>
+        <v>0.746</v>
       </c>
       <c r="R25" t="n">
-        <v>10.7</v>
+        <v>10.9</v>
       </c>
       <c r="S25" t="n">
-        <v>31.3</v>
+        <v>30.9</v>
       </c>
       <c r="T25" t="n">
-        <v>41.9</v>
+        <v>41.8</v>
       </c>
       <c r="U25" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="V25" t="n">
-        <v>15.8</v>
+        <v>16</v>
       </c>
       <c r="W25" t="n">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X25" t="n">
         <v>5</v>
@@ -4913,31 +4980,31 @@
         <v>3.7</v>
       </c>
       <c r="Z25" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>20.7</v>
+        <v>20.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>102.6</v>
+        <v>102.4</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AE25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG25" t="n">
         <v>8</v>
       </c>
       <c r="AH25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI25" t="n">
         <v>11</v>
@@ -4955,10 +5022,10 @@
         <v>3</v>
       </c>
       <c r="AN25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP25" t="n">
         <v>14</v>
@@ -4967,22 +5034,22 @@
         <v>21</v>
       </c>
       <c r="AR25" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AS25" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AT25" t="n">
         <v>20</v>
       </c>
       <c r="AU25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AV25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AX25" t="n">
         <v>12</v>
@@ -4994,13 +5061,13 @@
         <v>19</v>
       </c>
       <c r="BA25" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BB25" t="n">
         <v>11</v>
       </c>
       <c r="BC25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-15-2013-14</t>
+          <t>2013-12-15</t>
         </is>
       </c>
     </row>
@@ -5029,85 +5096,85 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F26" t="n">
         <v>4</v>
       </c>
       <c r="G26" t="n">
-        <v>0.84</v>
+        <v>0.833</v>
       </c>
       <c r="H26" t="n">
-        <v>48.4</v>
+        <v>48.2</v>
       </c>
       <c r="I26" t="n">
-        <v>39.8</v>
+        <v>39.7</v>
       </c>
       <c r="J26" t="n">
-        <v>86.59999999999999</v>
+        <v>86</v>
       </c>
       <c r="K26" t="n">
-        <v>0.459</v>
+        <v>0.462</v>
       </c>
       <c r="L26" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="M26" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="N26" t="n">
-        <v>0.412</v>
+        <v>0.419</v>
       </c>
       <c r="O26" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="P26" t="n">
-        <v>22.7</v>
+        <v>22.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="R26" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="S26" t="n">
         <v>32.6</v>
       </c>
       <c r="T26" t="n">
-        <v>45.6</v>
+        <v>45.5</v>
       </c>
       <c r="U26" t="n">
         <v>23.6</v>
       </c>
       <c r="V26" t="n">
-        <v>14.3</v>
+        <v>14.5</v>
       </c>
       <c r="W26" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="X26" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Z26" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="AB26" t="n">
-        <v>107.9</v>
+        <v>107.8</v>
       </c>
       <c r="AC26" t="n">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -5119,7 +5186,7 @@
         <v>2</v>
       </c>
       <c r="AH26" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AI26" t="n">
         <v>2</v>
@@ -5128,7 +5195,7 @@
         <v>4</v>
       </c>
       <c r="AK26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL26" t="n">
         <v>2</v>
@@ -5137,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="AN26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ26" t="n">
         <v>2</v>
@@ -5152,7 +5219,7 @@
         <v>4</v>
       </c>
       <c r="AS26" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AT26" t="n">
         <v>5</v>
@@ -5161,13 +5228,13 @@
         <v>6</v>
       </c>
       <c r="AV26" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AW26" t="n">
         <v>30</v>
       </c>
       <c r="AX26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY26" t="n">
         <v>3</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-15-2013-14</t>
+          <t>2013-12-15</t>
         </is>
       </c>
     </row>
@@ -5211,97 +5278,97 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F27" t="n">
         <v>15</v>
       </c>
       <c r="G27" t="n">
-        <v>0.318</v>
+        <v>0.286</v>
       </c>
       <c r="H27" t="n">
         <v>48.5</v>
       </c>
       <c r="I27" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="J27" t="n">
-        <v>84.09999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="K27" t="n">
-        <v>0.435</v>
+        <v>0.433</v>
       </c>
       <c r="L27" t="n">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="M27" t="n">
-        <v>20.9</v>
+        <v>21.2</v>
       </c>
       <c r="N27" t="n">
-        <v>0.331</v>
+        <v>0.334</v>
       </c>
       <c r="O27" t="n">
-        <v>19.4</v>
+        <v>19.1</v>
       </c>
       <c r="P27" t="n">
-        <v>24.5</v>
+        <v>24.3</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.791</v>
+        <v>0.788</v>
       </c>
       <c r="R27" t="n">
-        <v>11.5</v>
+        <v>11.8</v>
       </c>
       <c r="S27" t="n">
-        <v>30.9</v>
+        <v>30.7</v>
       </c>
       <c r="T27" t="n">
-        <v>42.5</v>
+        <v>42.4</v>
       </c>
       <c r="U27" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="V27" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="W27" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="X27" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Y27" t="n">
         <v>6.3</v>
       </c>
       <c r="Z27" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>22.2</v>
+        <v>22</v>
       </c>
       <c r="AB27" t="n">
-        <v>99.5</v>
+        <v>99.2</v>
       </c>
       <c r="AC27" t="n">
-        <v>-2.5</v>
+        <v>-3.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AE27" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AF27" t="n">
         <v>24</v>
       </c>
       <c r="AG27" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AH27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI27" t="n">
         <v>19</v>
@@ -5310,13 +5377,13 @@
         <v>10</v>
       </c>
       <c r="AK27" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AL27" t="n">
         <v>19</v>
       </c>
       <c r="AM27" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AN27" t="n">
         <v>25</v>
@@ -5325,25 +5392,25 @@
         <v>7</v>
       </c>
       <c r="AP27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ27" t="n">
         <v>5</v>
       </c>
       <c r="AR27" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AS27" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AT27" t="n">
         <v>18</v>
       </c>
       <c r="AU27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW27" t="n">
         <v>11</v>
@@ -5352,7 +5419,7 @@
         <v>29</v>
       </c>
       <c r="AY27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AZ27" t="n">
         <v>30</v>
@@ -5364,7 +5431,7 @@
         <v>17</v>
       </c>
       <c r="BC27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-15-2013-14</t>
+          <t>2013-12-15</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>10.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE28" t="n">
         <v>3</v>
@@ -5498,7 +5565,7 @@
         <v>8</v>
       </c>
       <c r="AM28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AN28" t="n">
         <v>3</v>
@@ -5519,7 +5586,7 @@
         <v>5</v>
       </c>
       <c r="AT28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU28" t="n">
         <v>1</v>
@@ -5543,7 +5610,7 @@
         <v>30</v>
       </c>
       <c r="BB28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC28" t="n">
         <v>1</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-15-2013-14</t>
+          <t>2013-12-15</t>
         </is>
       </c>
     </row>
@@ -5653,13 +5720,13 @@
         <v>0.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AE29" t="n">
         <v>20</v>
       </c>
       <c r="AF29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG29" t="n">
         <v>20</v>
@@ -5674,7 +5741,7 @@
         <v>15</v>
       </c>
       <c r="AK29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL29" t="n">
         <v>16</v>
@@ -5683,7 +5750,7 @@
         <v>14</v>
       </c>
       <c r="AN29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO29" t="n">
         <v>6</v>
@@ -5698,7 +5765,7 @@
         <v>7</v>
       </c>
       <c r="AS29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT29" t="n">
         <v>16</v>
@@ -5710,13 +5777,13 @@
         <v>13</v>
       </c>
       <c r="AW29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX29" t="n">
         <v>14</v>
       </c>
       <c r="AY29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ29" t="n">
         <v>26</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-15-2013-14</t>
+          <t>2013-12-15</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5905,7 @@
         <v>1</v>
       </c>
       <c r="AE30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF30" t="n">
         <v>30</v>
@@ -5847,7 +5914,7 @@
         <v>29</v>
       </c>
       <c r="AH30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI30" t="n">
         <v>26</v>
@@ -5856,7 +5923,7 @@
         <v>19</v>
       </c>
       <c r="AK30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL30" t="n">
         <v>27</v>
@@ -5865,10 +5932,10 @@
         <v>26</v>
       </c>
       <c r="AN30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP30" t="n">
         <v>19</v>
@@ -5904,7 +5971,7 @@
         <v>23</v>
       </c>
       <c r="BA30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB30" t="n">
         <v>27</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-15-2013-14</t>
+          <t>2013-12-15</t>
         </is>
       </c>
     </row>
@@ -6017,13 +6084,13 @@
         <v>-1.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AE31" t="n">
         <v>20</v>
       </c>
       <c r="AF31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG31" t="n">
         <v>20</v>
@@ -6053,16 +6120,16 @@
         <v>27</v>
       </c>
       <c r="AP31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ31" t="n">
         <v>24</v>
       </c>
       <c r="AR31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT31" t="n">
         <v>19</v>
@@ -6077,7 +6144,7 @@
         <v>6</v>
       </c>
       <c r="AX31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY31" t="n">
         <v>6</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-15-2013-14</t>
+          <t>2013-12-15</t>
         </is>
       </c>
     </row>
